--- a/TESTS/zlit_5_issumbosi.xlsx
+++ b/TESTS/zlit_5_issumbosi.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Іссумбосі — що означає «одна мізинна кістка», бо хлопчик був розміром з мізинець</t>
+          <t>Іссумбосі</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Бо він був розміром з мізинець — найменший можливий розмір людини</t>
+          <t>Бо він був розміром з мізинець</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Він надзвичайно маленький — розміром з мізинець хоча розумний і хоробрий</t>
+          <t>Він надзвичайно маленький</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Потрапити до столиці і стати самурайом — довести що розмір не визначає цінність людини</t>
+          <t>Потрапити до столиці і стати самурайом</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>До столиці — він мріяв служити знатній людині і довести свою хоробрість</t>
+          <t>До столиці</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Прагнення самореалізації — він не хотів залишатись малим хлопчиком у малому світі</t>
+          <t>Прагнення самореалізації</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Голкою замість меча і черепашкою як чашею — підручні предмети стали його зброєю і човном</t>
+          <t>Голкою замість меча і черепашкою як чашею</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -897,6 +937,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Мискою що плила по річці — він грібся паличками для їжі</t>
+          <t>Мискою що плила по річці</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Як з'явився на світ Іссумбосі, за казкою?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його знайшли в лісі</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Старе бездітне подружжя довго молилося богам про дитину, і народився крихітний хлопчик</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його приніс журавель</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він народився з квітки</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Як батьки ставились до того, що їхній син не росте, попри роки?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Соромились його</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Любили його так само сильно, хоч і журились, що він не росте</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Хотіли віддати в інший дім</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Не звертали уваги</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Чому, попри малий зріст, Іссумбосі вирішив вирушити в столицю саме сам?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Батьки прогнали його</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він сам прагнув довести, що зріст не визначає людину, і досягти чогось важливого</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Йому наказав імператор</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він заблукав і не зміг повернутись</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Як вельможа поставився до крихітного слуги, коли Іссумбосі прийшов найматися на службу?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Прогнав одразу</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Здивувався, але взяв його на службу, оцінивши кмітливість</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Не помітив його</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Висміяв і побив</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Чим Іссумбосі швидко заслужив повагу у домі вельможі?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Силою</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Розумом, старанністю і вмінням знаходити вихід там, де великі люди губилися</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Багатством</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Зростом</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Кого з родини вельможі особливо опікав Іссумбосі?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Самого вельможу</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Доньку вельможі, яку згодом мав супроводжувати в дорозі</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сторожа</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Кухаря</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Куди Іссумбосі супроводжував донечку вельможі, коли на них напав демон-они?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>На свято до сусіднього села</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У паломництво до храму</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>На полювання</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>На весілля</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Як демон-они спочатку поставився до крихітного Іссумбосі, що став на захист дівчини?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Злякався одразу</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зневажливо й насмішкувато — проковтнув маленького суперника, не сприйнявши його серйозно</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Втік без бою</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Запропонував дружбу</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що Іссумбосі зробив, опинившись у животі демона?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Заснув</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Голкою-мечем почав колоти демона зсередини, завдаючи болю</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Покликав на допомогу</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Спробував вилізти назовні крізь рот</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Що демон зробив від нестерпного болю всередині себе?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Проковтнув ще раз</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Виплюнув Іссумбосі і кинувся тікати</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Заснув</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Попросив пощади і залишився</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що демон-они залишив, утікаючи в паніці?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Свою зброю</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Чарівний молоток, що виконує бажання</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Мішок із золотом</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Своє вбрання</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Що першим спало на думку доньці вельможі, коли вона побачила чарівний молоток?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Викинути його</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Попросити молоток виконати бажання — щоб Іссумбосі став звичайного зросту</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Продати його</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сховати молоток назавжди</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Що сталося з Іссумбосі після того, як молоток виконав бажання?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він залишився таким самим</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він перетворився на високого красивого юнака звичайного зросту</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він зник</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він став ще меншим</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Як змінилося ставлення вельможі до Іссумбосі після цього перетворення?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Не змінилось</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вельможа з радістю погодився на шлюб Іссумбосі з його донькою</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вельможа прогнав його</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вельможа злякався</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Чи повернувся Іссумбосі до своїх старих батьків після перетворення?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ні, забув про них</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Так, він забрав їх до столиці, і вони щасливо жили разом</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Так, але лише ненадовго</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Невідомо</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Який європейський казковий персонаж найбільш подібний до Іссумбосі за сюжетом про крихітного героя?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Червона Шапочка</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Хлопчик-Мізинчик (Мальчик-с-пальчик)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Білосніжка</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Дюймовочка</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Що спільне для казок різних народів про крихітних героїв, подібних до Іссумбосі?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Усі вони закінчуються сумно</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Малий зріст героя протиставляється його великим розуму, хоробрості й добрим вчинкам</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Усі герої — дівчатка</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Усі живуть у морі</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Чому образ крихітного, але мужнього героя популярний у народних казках різних країн?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо такі казки коротші</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він дає надію кожній дитині: розмір не головне, головне — характер і вчинки</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо так легше малювати ілюстрації</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо це смішно</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Що символізує те, що Іссумбосі озброївся голкою замість справжнього меча?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бідність родини</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Винахідливість — герой використовує те, що має, замість того, чого йому не дано</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що він боягуз</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Що зброя йому не потрібна</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Чому миска для рису й паличка для їжі стали для Іссумбосі човном і веслом?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він випадково їх загубив у річці</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Для крихітної людини звичні побутові речі стають придатним «транспортом»</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Це подарунок богів</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він їх спеціально виготовив</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Яка головна думка випливає з усієї історії Іссумбосі?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Зріст людини — найголовніше в житті</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Розум, відвага і добре серце важать більше, ніж фізичні розміри чи сила</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Треба завжди залишатись маленьким</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Подорожі — це небезпечно</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>З якою відомою європейською казкою можна порівняти «Іссумбосі»?</t>
+          <t>«Іссумбосі» багато в чому подібна до європейських казок про крихітних героїв, як «Хлопчик-Мізинчик».</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яка характерна риса японської народної казки помітна в «Іссумбосі»?</t>
+          <t>У японських народних казках часто поєднуються побутові деталі (миска, голка) з фантастичними елементами (демони, чарівні предмети).</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>До якої країни належить казка «Іссумбосі»?</t>
+          <t>«Іссумбосі» — корейська народна казка.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,29 +2207,32 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Що таке «чарівний молоток» у цій казці і яку роль він відіграє?</t>
+          <t>Чарівний молоток виконав бажання, і Іссумбосі назавжди залишився крихітним.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яким став Іссумбосі наприкінці казки?</t>
+          <t>Наприкінці казки Іссумбосі стає юнаком звичайного зросту і одружується з донькою вельможі.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея казки «Іссумбосі»?</t>
+          <t>Головна ідея казки — розум, мужність і доброта важливіші за фізичний розмір чи силу.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,37 +2412,42 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які риси характеру Іссумбосі допомогли йому досягти мети?</t>
+          <t>Які предмети відіграли важливу роль у пригодах Іссумбосі?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Хоробрість</t>
+          <t>Голка замість меча</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Наполегливість</t>
+          <t>Чарівний молоток демона</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Велика фізична сила</t>
+          <t>Черепашка як чаша</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Вірність обов'язку</t>
+          <t>Велика рибина</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>А,Б,Г</t>
+          <t>А,Б,В</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Знатному вельможі — він вірно служив і захистив господареву доньку від демона-они</t>
+          <t>Знатному вельможі</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Страшного демона-они — хлопчик боровся з ним голкою і переміг незважаючи на різницю у розмірі</t>
+          <t>Страшного демона-они</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
